--- a/excel/universities/university-of-eastern-finland.xlsx
+++ b/excel/universities/university-of-eastern-finland.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.uef.fi/en/apply</t>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,7 +125,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Master's programmes taught in English</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -140,12 +140,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">Most UEF English-taught master's programmes use the national first joint application round in January.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -229,7 +229,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Master's programmes taught in English</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -239,12 +239,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -254,12 +254,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.uef.fi/en/apply</t>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Required enclosures due 2026-01-28; verified educational documents due 2026-05-29 for completed degrees and 2026-07-30 for graduating applicants.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -275,7 +275,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,30 +333,156 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Master's programmes taught in English</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary degree certificates are accepted at application stage.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uef.fi/en/apply</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most recent transcript with translations must be uploaded by 2026-01-28 for foreign-degree applicants graduating later.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If needed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required when educational documents are not in English Finnish or Swedish.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/verification-of-official-educational-documents</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language proof must remain verifiable during the application period.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/degree-programme/masters-degree-programme-in-english-language-and-culture</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +495,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +546,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -437,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Eastern Finland</t>
+          <t xml:space="preserve">University Name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +598,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -482,7 +623,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.uef.fi/en</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -492,7 +633,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/excel/universities/university-of-eastern-finland.xlsx
+++ b/excel/universities/university-of-eastern-finland.xlsx
@@ -495,7 +495,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,17 +578,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">University Name</t>
+          <t xml:space="preserve">University of Eastern Finland</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">School of Computing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Pauli Miettinen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Data mining; Machine learning; Discrete optimization; Pattern discovery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">UEF official profile</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.uef.fi/en/person/pauli.miettinen</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -648,7 +648,161 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markku Tukiainen</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Human-computer interaction; Learning technologies; Computer science education</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/markku.tukiainen</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ville Hautamaki</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speech processing; Speaker recognition; Biometrics; Audio analysis</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/ville.hautamaki</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
         </is>
       </c>
     </row>

--- a/excel/universities/university-of-eastern-finland.xlsx
+++ b/excel/universities/university-of-eastern-finland.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -495,7 +496,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,70 +507,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">department_name</t>
+          <t xml:space="preserve">unit_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">professor_name</t>
+          <t xml:space="preserve">unit_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">parent_unit</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">research_areas</t>
+          <t xml:space="preserve">campus_or_city</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">researchgate_url</t>
+          <t xml:space="preserve">focus_areas</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">google_scholar_url</t>
+          <t xml:space="preserve">official_url</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation_count</t>
+          <t xml:space="preserve">notes</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">h_index</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation_source</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation_last_checked</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">official_profile_url</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">email</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">notes</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -583,72 +554,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Computing</t>
+          <t xml:space="preserve">Faculty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pauli Miettinen</t>
+          <t xml:space="preserve">Philosophical Faculty</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data mining; Machine learning; Discrete optimization; Pattern discovery</t>
+          <t xml:space="preserve">Joensuu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Education; Humanities; Theology</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official organisation page.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uef.fi/en/person/pauli.miettinen</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
@@ -660,72 +601,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Computing</t>
+          <t xml:space="preserve">Faculty</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markku Tukiainen</t>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human-computer interaction; Learning technologies; Computer science education</t>
+          <t xml:space="preserve">Joensuu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Science; Forestry; Technology</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official organisation page.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uef.fi/en/person/markku.tukiainen</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
@@ -737,9 +648,532 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t xml:space="preserve">School of Computing</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Forest Sciences</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forest sciences</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Pharmacy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuopio</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pharmacy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Applied Educational Science and Teacher Education</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophical Faculty</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teacher education</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health Sciences</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuopio</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine; Public health; Nursing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organisation page.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences and Business Studies</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuopio</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business; Law; Social sciences</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organisation page.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">department_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">professor_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">research_areas</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">researchgate_url</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">google_scholar_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h_index</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_profile_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pauli Miettinen</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data mining; Machine learning; Discrete optimization; Pattern discovery</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/pauli.miettinen</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markku Tukiainen</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Human-computer interaction; Learning technologies; Computer science education</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/markku.tukiainen</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ville Hautamaki</t>
@@ -803,6 +1237,83 @@
       <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pasi Franti</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine learning; Pattern recognition; Data mining; Time series</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/pasi.franti</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official UEF profile used for title and research-focus mapping.</t>
         </is>
       </c>
     </row>
